--- a/IA_supervised/importancia_var_rf.xlsx
+++ b/IA_supervised/importancia_var_rf.xlsx
@@ -1,80 +1,118 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\crist\Desktop\codigo_TFM\Generacion_librerias_IA_prediccion_ciliopatias\IA_supervised\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF0DEF0E-0306-4FBD-B81A-5575316953CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Overall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aural.Anomalies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cerebral.Anomalies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coronary.and.Vascular.Anomalies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Digestive.Anomalies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Facial.Anomalies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hormonal.Anomalies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liver.Anomalies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nasal.Anomalies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Neural.Anomalies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ophthalmic.Anomalies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Organ.Anomalies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Others</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Renal.Anomalies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reproductive.Anomalies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Respiratory.Anomalies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skeletal.Anomalies</t>
+    <t>Aural.Anomalies</t>
+  </si>
+  <si>
+    <t>Cerebral.Anomalies</t>
+  </si>
+  <si>
+    <t>Coronary.and.Vascular.Anomalies</t>
+  </si>
+  <si>
+    <t>Digestive.Anomalies</t>
+  </si>
+  <si>
+    <t>Facial.Anomalies</t>
+  </si>
+  <si>
+    <t>Hormonal.Anomalies</t>
+  </si>
+  <si>
+    <t>Liver.Anomalies</t>
+  </si>
+  <si>
+    <t>Nasal.Anomalies</t>
+  </si>
+  <si>
+    <t>Neural.Anomalies</t>
+  </si>
+  <si>
+    <t>Ophthalmic.Anomalies</t>
+  </si>
+  <si>
+    <t>Organ.Anomalies</t>
+  </si>
+  <si>
+    <t>Others</t>
+  </si>
+  <si>
+    <t>Renal.Anomalies</t>
+  </si>
+  <si>
+    <t>Reproductive.Anomalies</t>
+  </si>
+  <si>
+    <t>Respiratory.Anomalies</t>
+  </si>
+  <si>
+    <t>Skeletal.Anomalies</t>
+  </si>
+  <si>
+    <t>Variables</t>
+  </si>
+  <si>
+    <t>Dis.Media</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <numFmts count="1">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -90,7 +128,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -98,17 +136,47 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Millares" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -390,148 +458,155 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="31.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="3">
+        <v>41.398891842270203</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="3">
+        <v>36.745826346224099</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="3">
+        <v>27.786848278258599</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="3">
+        <v>24.8808485886344</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="3">
+        <v>24.752638410072301</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="3">
+        <v>16.584400623317901</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="3">
+        <v>15.435311374089499</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="3">
+        <v>14.2872454196044</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="n">
-        <v>10.2970980129269</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="n">
-        <v>14.2872454196044</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
+      <c r="B11" s="3">
+        <v>10.297098012926901</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="3">
+        <v>7.9539134350956502</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3">
+        <v>7.8379927679905199</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="3">
+        <v>3.7994054426958699</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="3">
+        <v>2.1179014983685698</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" s="3">
+        <v>1.3819121407809001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B4" t="n">
-        <v>24.8808485886344</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" t="n">
-        <v>16.5844006233179</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" t="n">
+      <c r="B17" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" t="n">
-        <v>41.3988918422702</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" t="n">
-        <v>15.4353113740895</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" t="n">
-        <v>7.95391343509565</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" t="n">
-        <v>27.7868482782586</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" t="n">
-        <v>36.7458263462241</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" t="n">
-        <v>1.3819121407809</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" t="n">
-        <v>7.83799276799052</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" t="n">
-        <v>2.11790149836857</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" t="n">
-        <v>24.7526384100723</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17" t="n">
-        <v>3.79940544269587</v>
-      </c>
-    </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B17">
+    <sortCondition descending="1" ref="B2:B17"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>